--- a/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
@@ -656,7 +656,7 @@
         <v>2017</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -724,7 +724,7 @@
         <v>2018</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>6313000</v>
+        <v>2946000</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -792,7 +792,7 @@
         <v>2019</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1005697000</v>
+        <v>308136000</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -860,7 +860,7 @@
         <v>2020</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>14012473000</v>
+        <v>6545891000</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -928,7 +928,7 @@
         <v>2021</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>185111963000</v>
+        <v>127962565000</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -996,7 +996,7 @@
         <v>2022</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>621795347000</v>
+        <v>555473424000</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>2023</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>3025765385000</v>
+        <v>2268481045000</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1132,7 +1132,7 @@
         <v>2024</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>4963355551000</v>
+        <v>4254217264000</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1200,7 +1200,7 @@
         <v>2025</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>16489790761000</v>
+        <v>16611808046000</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1268,7 +1268,7 @@
         <v>2026</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>89759368949000</v>
+        <v>107727225619000</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1336,7 +1336,7 @@
         <v>2027</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>184820483420000</v>
+        <v>294678468053000</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>184820483420000</v>
+        <v>294678468053000</v>
       </c>
     </row>
     <row r="18">

--- a/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
